--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991E94D5-239B-4F77-AC8C-31679604150A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2848CB-9911-492A-8EA1-D00A7C01D3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1015,88 +1015,88 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="D8">
         <v>0.1</v>
       </c>
       <c r="F8">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G8">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="H8">
         <v>0.5</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="M8">
-        <v>486</v>
+        <v>600</v>
       </c>
       <c r="N8">
         <v>2</v>
       </c>
       <c r="O8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8">
         <f t="shared" si="2"/>
-        <v>562</v>
+        <v>440</v>
       </c>
       <c r="Q8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <f t="shared" si="4"/>
-        <v>7.3901956737395054E-6</v>
+        <v>8.0093296961816622E-6</v>
       </c>
       <c r="T8">
         <f t="shared" si="5"/>
-        <v>4.2021551106583754E-8</v>
+        <v>4.364626552580502E-8</v>
       </c>
       <c r="U8">
         <f t="shared" si="6"/>
-        <v>1.759570398509406E-3</v>
+        <v>1.9069832609956339E-3</v>
       </c>
       <c r="V8">
         <f t="shared" si="7"/>
-        <v>4.307266616881891E-5</v>
+        <v>4.6578420007594534E-5</v>
       </c>
       <c r="W8">
         <f t="shared" si="8"/>
-        <v>1.6978851963746224</v>
+        <v>1.3293051359516617</v>
       </c>
       <c r="X8">
         <f t="shared" si="9"/>
-        <v>1.2353763403938013E-2</v>
+        <v>1.5238618895658656E-2</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D9">
         <v>0.1</v>
@@ -1105,137 +1105,137 @@
         <v>198</v>
       </c>
       <c r="G9">
-        <v>461</v>
+        <v>502.5</v>
       </c>
       <c r="H9">
         <v>0.5</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>263</v>
+        <v>304.5</v>
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1016</v>
+        <v>980</v>
       </c>
       <c r="M9">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="N9">
         <v>2</v>
       </c>
       <c r="O9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <f t="shared" si="2"/>
-        <v>636</v>
+        <v>576</v>
       </c>
       <c r="Q9">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <f t="shared" si="4"/>
-        <v>8.7842351369405489E-6</v>
+        <v>1.0204355198691699E-5</v>
       </c>
       <c r="T9">
         <f t="shared" si="5"/>
-        <v>4.5281404465810625E-8</v>
+        <v>4.8911444595405938E-8</v>
       </c>
       <c r="U9">
         <f t="shared" si="6"/>
-        <v>2.0914845564144165E-3</v>
+        <v>2.4296083806408806E-3</v>
       </c>
       <c r="V9">
         <f t="shared" si="7"/>
-        <v>5.0950980225292664E-5</v>
+        <v>5.9008386661903181E-5</v>
       </c>
       <c r="W9">
         <f t="shared" si="8"/>
-        <v>1.9214501510574018</v>
+        <v>1.7401812688821752</v>
       </c>
       <c r="X9">
         <f t="shared" si="9"/>
-        <v>1.242826741913804E-2</v>
+        <v>2.4311712998973202E-2</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>29.9</v>
+        <v>30.4</v>
       </c>
       <c r="D10">
         <v>0.1</v>
       </c>
       <c r="F10">
-        <v>198</v>
+        <v>197.5</v>
       </c>
       <c r="G10">
-        <v>502.5</v>
+        <v>536.5</v>
       </c>
       <c r="H10">
         <v>0.5</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>304.5</v>
+        <v>339</v>
       </c>
       <c r="J10">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L10">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="M10">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="N10">
         <v>2</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P10">
         <f t="shared" si="2"/>
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="Q10">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S10">
         <f t="shared" si="4"/>
-        <v>1.0204355198691699E-5</v>
+        <v>1.1173663115705097E-5</v>
       </c>
       <c r="T10">
         <f t="shared" si="5"/>
-        <v>4.8911444595405938E-8</v>
+        <v>5.0623327338103899E-8</v>
       </c>
       <c r="U10">
         <f t="shared" si="6"/>
-        <v>2.4296083806408806E-3</v>
+        <v>2.6603959799297852E-3</v>
       </c>
       <c r="V10">
         <f t="shared" si="7"/>
-        <v>5.9008386661903181E-5</v>
+        <v>6.4479333191259661E-5</v>
       </c>
       <c r="W10">
         <f t="shared" si="8"/>
-        <v>1.7401812688821752</v>
+        <v>1.8006042296072509</v>
       </c>
       <c r="X10">
         <f t="shared" si="9"/>
-        <v>2.4311712998973202E-2</v>
+        <v>1.2386907336791842E-2</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.3">

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2848CB-9911-492A-8EA1-D00A7C01D3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF66884-D839-4E23-AF68-53FAB7D59711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="7.5546875" customWidth="1"/>
@@ -568,11 +568,11 @@
         <v>0.5</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I11" si="0">G2-F2</f>
+        <f t="shared" ref="I2:I12" si="0">G2-F2</f>
         <v>75.5</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J11" si="1">2*H2</f>
+        <f t="shared" ref="J2:J12" si="1">2*H2</f>
         <v>1</v>
       </c>
       <c r="L2">
@@ -588,35 +588,35 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <f t="shared" ref="P2:P11" si="2">L2-M2</f>
+        <f t="shared" ref="P2:P12" si="2">L2-M2</f>
         <v>145</v>
       </c>
       <c r="Q2">
-        <f t="shared" ref="Q2:Q11" si="3">O2+N2</f>
+        <f t="shared" ref="Q2:Q12" si="3">O2+N2</f>
         <v>4</v>
       </c>
       <c r="S2">
-        <f t="shared" ref="S2:S11" si="4">(I2/10^3)/($AD$2*C2)</f>
+        <f t="shared" ref="S2:S12" si="4">(I2/10^3)/($AD$2*C2)</f>
         <v>2.5050100200400804E-6</v>
       </c>
       <c r="T2">
-        <f t="shared" ref="T2:T11" si="5">S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
+        <f t="shared" ref="T2:T12" si="5">S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
         <v>3.4292054268838759E-8</v>
       </c>
       <c r="U2">
-        <f t="shared" ref="U2:U11" si="6">S2/($Z$2/10^6)</f>
+        <f t="shared" ref="U2:U12" si="6">S2/($Z$2/10^6)</f>
         <v>5.964309571524001E-4</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:V11" si="7">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
+        <f t="shared" ref="V2:V12" si="7">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
         <v>1.6380612974879218E-5</v>
       </c>
       <c r="W2">
-        <f t="shared" ref="W2:W11" si="8">P2/$AB$2</f>
+        <f t="shared" ref="W2:W12" si="8">P2/$AB$2</f>
         <v>0.4380664652567976</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X11" si="9">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
+        <f t="shared" ref="X2:X12" si="9">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
         <v>1.2102696241490761E-2</v>
       </c>
       <c r="Z2">
@@ -1243,89 +1243,164 @@
         <v>26</v>
       </c>
       <c r="B11">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="D11">
         <v>0.1</v>
       </c>
       <c r="F11">
-        <v>198</v>
+        <v>199.5</v>
       </c>
       <c r="G11">
-        <v>574</v>
+        <v>576.5</v>
       </c>
       <c r="H11">
         <v>0.5</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L11">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="M11">
-        <v>279</v>
+        <v>174</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <f t="shared" si="2"/>
-        <v>663</v>
+        <v>752</v>
       </c>
       <c r="Q11">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S11">
         <f t="shared" si="4"/>
-        <v>1.2600451739599601E-5</v>
+        <v>1.259185036740147E-5</v>
       </c>
       <c r="T11">
         <f t="shared" si="5"/>
-        <v>5.5302786380944353E-8</v>
+        <v>5.5104251991726919E-8</v>
       </c>
       <c r="U11">
         <f t="shared" si="6"/>
-        <v>3.0001075570475241E-3</v>
+        <v>2.9980596112860643E-3</v>
       </c>
       <c r="V11">
         <f t="shared" si="7"/>
-        <v>7.2634600879331815E-5</v>
+        <v>7.2578088728497025E-5</v>
       </c>
       <c r="W11">
         <f t="shared" si="8"/>
-        <v>2.0030211480362539</v>
+        <v>2.2719033232628401</v>
       </c>
       <c r="X11">
         <f t="shared" si="9"/>
+        <v>3.6415849479503985E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>29.9</v>
+      </c>
+      <c r="D12">
+        <v>0.1</v>
+      </c>
+      <c r="F12">
+        <v>198</v>
+      </c>
+      <c r="G12">
+        <v>574</v>
+      </c>
+      <c r="H12">
+        <v>0.5</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>376</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>942</v>
+      </c>
+      <c r="M12">
+        <v>279</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="2"/>
+        <v>663</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="4"/>
+        <v>1.2600451739599601E-5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="5"/>
+        <v>5.5302786380944353E-8</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="6"/>
+        <v>3.0001075570475241E-3</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="7"/>
+        <v>7.2634600879331815E-5</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="8"/>
+        <v>2.0030211480362539</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="9"/>
         <v>1.2457620102851751E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="L15" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="S16" t="s">
+      <c r="L16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="19:19" x14ac:dyDescent="0.3">
+      <c r="S17" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X12">
-    <sortCondition ref="A2:A12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X13">
+    <sortCondition ref="A2:A13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF66884-D839-4E23-AF68-53FAB7D59711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFB0CA4-74B8-4954-8B65-E9703D0A351A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="7.5546875" customWidth="1"/>
@@ -568,11 +568,11 @@
         <v>0.5</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I12" si="0">G2-F2</f>
+        <f t="shared" ref="I2:I11" si="0">G2-F2</f>
         <v>75.5</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J12" si="1">2*H2</f>
+        <f t="shared" ref="J2:J11" si="1">2*H2</f>
         <v>1</v>
       </c>
       <c r="L2">
@@ -588,35 +588,35 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <f t="shared" ref="P2:P12" si="2">L2-M2</f>
+        <f t="shared" ref="P2:P11" si="2">L2-M2</f>
         <v>145</v>
       </c>
       <c r="Q2">
-        <f t="shared" ref="Q2:Q12" si="3">O2+N2</f>
+        <f t="shared" ref="Q2:Q11" si="3">O2+N2</f>
         <v>4</v>
       </c>
       <c r="S2">
-        <f t="shared" ref="S2:S12" si="4">(I2/10^3)/($AD$2*C2)</f>
+        <f t="shared" ref="S2:S11" si="4">(I2/10^3)/($AD$2*C2)</f>
         <v>2.5050100200400804E-6</v>
       </c>
       <c r="T2">
-        <f t="shared" ref="T2:T12" si="5">S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
+        <f t="shared" ref="T2:T11" si="5">S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
         <v>3.4292054268838759E-8</v>
       </c>
       <c r="U2">
-        <f t="shared" ref="U2:U12" si="6">S2/($Z$2/10^6)</f>
+        <f t="shared" ref="U2:U11" si="6">S2/($Z$2/10^6)</f>
         <v>5.964309571524001E-4</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:V12" si="7">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
+        <f t="shared" ref="V2:V11" si="7">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
         <v>1.6380612974879218E-5</v>
       </c>
       <c r="W2">
-        <f t="shared" ref="W2:W12" si="8">P2/$AB$2</f>
+        <f t="shared" ref="W2:W11" si="8">P2/$AB$2</f>
         <v>0.4380664652567976</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X12" si="9">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
+        <f t="shared" ref="X2:X11" si="9">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
         <v>1.2102696241490761E-2</v>
       </c>
       <c r="Z2">
@@ -1243,164 +1243,89 @@
         <v>26</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D11">
         <v>0.1</v>
       </c>
       <c r="F11">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="G11">
-        <v>576.5</v>
+        <v>574</v>
       </c>
       <c r="H11">
         <v>0.5</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L11">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="M11">
-        <v>174</v>
+        <v>279</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
       <c r="O11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P11">
         <f t="shared" si="2"/>
-        <v>752</v>
+        <v>663</v>
       </c>
       <c r="Q11">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <f t="shared" si="4"/>
-        <v>1.259185036740147E-5</v>
+        <v>1.2600451739599601E-5</v>
       </c>
       <c r="T11">
         <f t="shared" si="5"/>
-        <v>5.5104251991726919E-8</v>
+        <v>5.5302786380944353E-8</v>
       </c>
       <c r="U11">
         <f t="shared" si="6"/>
-        <v>2.9980596112860643E-3</v>
+        <v>3.0001075570475241E-3</v>
       </c>
       <c r="V11">
         <f t="shared" si="7"/>
-        <v>7.2578088728497025E-5</v>
+        <v>7.2634600879331815E-5</v>
       </c>
       <c r="W11">
         <f t="shared" si="8"/>
-        <v>2.2719033232628401</v>
+        <v>2.0030211480362539</v>
       </c>
       <c r="X11">
         <f t="shared" si="9"/>
-        <v>3.6415849479503985E-2</v>
+        <v>1.2457620102851751E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>26</v>
-      </c>
-      <c r="B12">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>29.9</v>
-      </c>
-      <c r="D12">
-        <v>0.1</v>
-      </c>
-      <c r="F12">
-        <v>198</v>
-      </c>
-      <c r="G12">
-        <v>574</v>
-      </c>
-      <c r="H12">
-        <v>0.5</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="0"/>
-        <v>376</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>942</v>
-      </c>
-      <c r="M12">
-        <v>279</v>
-      </c>
-      <c r="N12">
-        <v>2</v>
-      </c>
-      <c r="O12">
-        <v>2</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="2"/>
-        <v>663</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="4"/>
-        <v>1.2600451739599601E-5</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="5"/>
-        <v>5.5302786380944353E-8</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="6"/>
-        <v>3.0001075570475241E-3</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="7"/>
-        <v>7.2634600879331815E-5</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="8"/>
-        <v>2.0030211480362539</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="9"/>
-        <v>1.2457620102851751E-2</v>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="L15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="L16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S17" t="s">
+      <c r="S16" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X13">
-    <sortCondition ref="A2:A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X12">
+    <sortCondition ref="A2:A12"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFB0CA4-74B8-4954-8B65-E9703D0A351A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652E0410-0B61-42C5-9EF2-F106629EC512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652E0410-0B61-42C5-9EF2-F106629EC512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6957C43-8293-4FAA-BD57-4BA8B38FD66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6957C43-8293-4FAA-BD57-4BA8B38FD66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFEC7A9-3CF3-40CB-B9A5-60E90212EA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,9 +99,6 @@
     <t>débit_(m^3/s)</t>
   </si>
   <si>
-    <t>flux_Darcy_(m/s)</t>
-  </si>
-  <si>
     <t>vitesse</t>
   </si>
   <si>
@@ -109,6 +106,9 @@
   </si>
   <si>
     <t>tare_(g)</t>
+  </si>
+  <si>
+    <t>flux_Darcy_(mm/s)</t>
   </si>
 </sst>
 </file>
@@ -448,7 +448,7 @@
     <col min="18" max="18" width="2.109375" customWidth="1"/>
     <col min="19" max="19" width="12.5546875" customWidth="1"/>
     <col min="20" max="20" width="10.109375" customWidth="1"/>
-    <col min="21" max="21" width="14.88671875" customWidth="1"/>
+    <col min="21" max="21" width="15.88671875" customWidth="1"/>
     <col min="22" max="22" width="8.33203125" customWidth="1"/>
     <col min="23" max="23" width="7.44140625" customWidth="1"/>
     <col min="24" max="24" width="7.77734375" customWidth="1"/>
@@ -463,7 +463,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
         <v>18</v>
@@ -499,7 +499,7 @@
         <v>22</v>
       </c>
       <c r="O1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P1" t="s">
         <v>11</v>
@@ -515,7 +515,7 @@
         <v>4</v>
       </c>
       <c r="U1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>5</v>
@@ -604,19 +604,19 @@
         <v>3.4292054268838759E-8</v>
       </c>
       <c r="U2">
-        <f t="shared" ref="U2:U11" si="6">S2/($Z$2/10^6)</f>
-        <v>5.964309571524001E-4</v>
+        <f>S2/($Z$2/10^6)*10^3</f>
+        <v>0.59643095715240013</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:V11" si="7">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
-        <v>1.6380612974879218E-5</v>
+        <f t="shared" ref="V2:V11" si="6">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
+        <v>1.6380612974879218E-2</v>
       </c>
       <c r="W2">
-        <f t="shared" ref="W2:W11" si="8">P2/$AB$2</f>
+        <f t="shared" ref="W2:W11" si="7">P2/$AB$2</f>
         <v>0.4380664652567976</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X11" si="9">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
+        <f t="shared" ref="X2:X11" si="8">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
         <v>1.2102696241490761E-2</v>
       </c>
       <c r="Z2">
@@ -697,19 +697,19 @@
         <v>3.5442652785390082E-8</v>
       </c>
       <c r="U3">
+        <f t="shared" ref="U3:U11" si="9">S3/($Z$2/10^6)*10^3</f>
+        <v>0.81114610172726409</v>
+      </c>
+      <c r="V3">
         <f t="shared" si="6"/>
-        <v>8.1114610172726409E-4</v>
-      </c>
-      <c r="V3">
+        <v>2.1076151770803291E-2</v>
+      </c>
+      <c r="W3">
         <f t="shared" si="7"/>
-        <v>2.1076151770803291E-5</v>
-      </c>
-      <c r="W3">
+        <v>0.55287009063444104</v>
+      </c>
+      <c r="X3">
         <f t="shared" si="8"/>
-        <v>0.55287009063444104</v>
-      </c>
-      <c r="X3">
-        <f t="shared" si="9"/>
         <v>1.2113415902573529E-2</v>
       </c>
     </row>
@@ -772,19 +772,19 @@
         <v>3.6471229298589113E-8</v>
       </c>
       <c r="U4">
+        <f t="shared" si="9"/>
+        <v>0.98141816360863177</v>
+      </c>
+      <c r="V4">
         <f t="shared" si="6"/>
-        <v>9.8141816360863181E-4</v>
-      </c>
-      <c r="V4">
+        <v>2.4928431214823365E-2</v>
+      </c>
+      <c r="W4">
         <f t="shared" si="7"/>
-        <v>2.4928431214823366E-5</v>
-      </c>
-      <c r="W4">
+        <v>0.68277945619335345</v>
+      </c>
+      <c r="X4">
         <f t="shared" si="8"/>
-        <v>0.68277945619335345</v>
-      </c>
-      <c r="X4">
-        <f t="shared" si="9"/>
         <v>1.2128525482848011E-2</v>
       </c>
     </row>
@@ -847,19 +847,19 @@
         <v>3.7257086899611824E-8</v>
       </c>
       <c r="U5">
+        <f t="shared" si="9"/>
+        <v>1.1292426122085439</v>
+      </c>
+      <c r="V5">
         <f t="shared" si="6"/>
-        <v>1.129242612208544E-3</v>
-      </c>
-      <c r="V5">
+        <v>2.8312296408463423E-2</v>
+      </c>
+      <c r="W5">
         <f t="shared" si="7"/>
-        <v>2.8312296408463423E-5</v>
-      </c>
-      <c r="W5">
+        <v>0.77039274924471302</v>
+      </c>
+      <c r="X5">
         <f t="shared" si="8"/>
-        <v>0.77039274924471302</v>
-      </c>
-      <c r="X5">
-        <f t="shared" si="9"/>
         <v>1.2140496163327807E-2</v>
       </c>
     </row>
@@ -922,19 +922,19 @@
         <v>3.810395820831726E-8</v>
       </c>
       <c r="U6">
+        <f t="shared" si="9"/>
+        <v>1.272121842165584</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="6"/>
-        <v>1.272121842165584E-3</v>
-      </c>
-      <c r="V6">
+        <v>3.1618161422865852E-2</v>
+      </c>
+      <c r="W6">
         <f t="shared" si="7"/>
-        <v>3.1618161422865852E-5</v>
-      </c>
-      <c r="W6">
+        <v>0.8821752265861027</v>
+      </c>
+      <c r="X6">
         <f t="shared" si="8"/>
-        <v>0.8821752265861027</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="9"/>
         <v>1.215784380647268E-2</v>
       </c>
     </row>
@@ -997,19 +997,19 @@
         <v>4.0454932254959881E-8</v>
       </c>
       <c r="U7">
+        <f t="shared" si="9"/>
+        <v>1.5772725644296026</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="6"/>
-        <v>1.5772725644296027E-3</v>
-      </c>
-      <c r="V7">
+        <v>3.8769691046076256E-2</v>
+      </c>
+      <c r="W7">
         <f t="shared" si="7"/>
-        <v>3.8769691046076259E-5</v>
-      </c>
-      <c r="W7">
+        <v>1.1057401812688821</v>
+      </c>
+      <c r="X7">
         <f t="shared" si="8"/>
-        <v>1.1057401812688821</v>
-      </c>
-      <c r="X7">
-        <f t="shared" si="9"/>
         <v>1.8203680576191282E-2</v>
       </c>
     </row>
@@ -1072,19 +1072,19 @@
         <v>4.364626552580502E-8</v>
       </c>
       <c r="U8">
+        <f t="shared" si="9"/>
+        <v>1.9069832609956339</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="6"/>
-        <v>1.9069832609956339E-3</v>
-      </c>
-      <c r="V8">
+        <v>4.6578420007594531E-2</v>
+      </c>
+      <c r="W8">
         <f t="shared" si="7"/>
-        <v>4.6578420007594534E-5</v>
-      </c>
-      <c r="W8">
+        <v>1.3293051359516617</v>
+      </c>
+      <c r="X8">
         <f t="shared" si="8"/>
-        <v>1.3293051359516617</v>
-      </c>
-      <c r="X8">
-        <f t="shared" si="9"/>
         <v>1.5238618895658656E-2</v>
       </c>
     </row>
@@ -1147,19 +1147,19 @@
         <v>4.8911444595405938E-8</v>
       </c>
       <c r="U9">
+        <f t="shared" si="9"/>
+        <v>2.4296083806408806</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="6"/>
-        <v>2.4296083806408806E-3</v>
-      </c>
-      <c r="V9">
+        <v>5.9008386661903181E-2</v>
+      </c>
+      <c r="W9">
         <f t="shared" si="7"/>
-        <v>5.9008386661903181E-5</v>
-      </c>
-      <c r="W9">
+        <v>1.7401812688821752</v>
+      </c>
+      <c r="X9">
         <f t="shared" si="8"/>
-        <v>1.7401812688821752</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="9"/>
         <v>2.4311712998973202E-2</v>
       </c>
     </row>
@@ -1222,19 +1222,19 @@
         <v>5.0623327338103899E-8</v>
       </c>
       <c r="U10">
+        <f t="shared" si="9"/>
+        <v>2.6603959799297852</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="6"/>
-        <v>2.6603959799297852E-3</v>
-      </c>
-      <c r="V10">
+        <v>6.4479333191259661E-2</v>
+      </c>
+      <c r="W10">
         <f t="shared" si="7"/>
-        <v>6.4479333191259661E-5</v>
-      </c>
-      <c r="W10">
+        <v>1.8006042296072509</v>
+      </c>
+      <c r="X10">
         <f t="shared" si="8"/>
-        <v>1.8006042296072509</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="9"/>
         <v>1.2386907336791842E-2</v>
       </c>
     </row>
@@ -1297,19 +1297,19 @@
         <v>5.5302786380944353E-8</v>
       </c>
       <c r="U11">
+        <f t="shared" si="9"/>
+        <v>3.000107557047524</v>
+      </c>
+      <c r="V11">
         <f t="shared" si="6"/>
-        <v>3.0001075570475241E-3</v>
-      </c>
-      <c r="V11">
+        <v>7.2634600879331809E-2</v>
+      </c>
+      <c r="W11">
         <f t="shared" si="7"/>
-        <v>7.2634600879331815E-5</v>
-      </c>
-      <c r="W11">
+        <v>2.0030211480362539</v>
+      </c>
+      <c r="X11">
         <f t="shared" si="8"/>
-        <v>2.0030211480362539</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="9"/>
         <v>1.2457620102851751E-2</v>
       </c>
     </row>

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFEC7A9-3CF3-40CB-B9A5-60E90212EA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1296139D-391B-4936-A149-FEBC96ED527D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -448,7 +448,7 @@
     <col min="18" max="18" width="2.109375" customWidth="1"/>
     <col min="19" max="19" width="12.5546875" customWidth="1"/>
     <col min="20" max="20" width="10.109375" customWidth="1"/>
-    <col min="21" max="21" width="15.88671875" customWidth="1"/>
+    <col min="21" max="21" width="17.109375" customWidth="1"/>
     <col min="22" max="22" width="8.33203125" customWidth="1"/>
     <col min="23" max="23" width="7.44140625" customWidth="1"/>
     <col min="24" max="24" width="7.77734375" customWidth="1"/>

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1296139D-391B-4936-A149-FEBC96ED527D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0120C9FC-2F7D-4900-ABA7-558EAA3BE3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/loi_darcy_corrige.xlsx
+++ b/loi_darcy_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0120C9FC-2F7D-4900-ABA7-558EAA3BE3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5CA8FE-38A7-4454-8B5B-3CCF7F2B699C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -609,7 +609,7 @@
       </c>
       <c r="V2">
         <f t="shared" ref="V2:V11" si="6">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
-        <v>1.6380612974879218E-2</v>
+        <v>2.2812291605106439E-2</v>
       </c>
       <c r="W2">
         <f t="shared" ref="W2:W11" si="7">P2/$AB$2</f>
@@ -623,7 +623,7 @@
         <v>4200</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AB2">
         <v>331</v>
@@ -702,7 +702,7 @@
       </c>
       <c r="V3">
         <f t="shared" si="6"/>
-        <v>2.1076151770803291E-2</v>
+        <v>3.0173568759096249E-2</v>
       </c>
       <c r="W3">
         <f t="shared" si="7"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="V4">
         <f t="shared" si="6"/>
-        <v>2.4928431214823365E-2</v>
+        <v>3.611029403408355E-2</v>
       </c>
       <c r="W4">
         <f t="shared" si="7"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="V5">
         <f t="shared" si="6"/>
-        <v>2.8312296408463423E-2</v>
+        <v>4.1294144428131001E-2</v>
       </c>
       <c r="W5">
         <f t="shared" si="7"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="V6">
         <f t="shared" si="6"/>
-        <v>3.1618161422865852E-2</v>
+        <v>4.632988670360029E-2</v>
       </c>
       <c r="W6">
         <f t="shared" si="7"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="V7">
         <f t="shared" si="6"/>
-        <v>3.8769691046076256E-2</v>
+        <v>5.7148733948822382E-2</v>
       </c>
       <c r="W7">
         <f t="shared" si="7"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="V8">
         <f t="shared" si="6"/>
-        <v>4.6578420007594531E-2</v>
+        <v>6.889480731685374E-2</v>
       </c>
       <c r="W8">
         <f t="shared" si="7"/>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="V9">
         <f t="shared" si="6"/>
-        <v>5.9008386661903181E-2</v>
+        <v>8.754971353744441E-2</v>
       </c>
       <c r="W9">
         <f t="shared" si="7"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="V10">
         <f t="shared" si="6"/>
-        <v>6.4479333191259661E-2</v>
+        <v>9.5775603314575297E-2</v>
       </c>
       <c r="W10">
         <f t="shared" si="7"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="V11">
         <f t="shared" si="6"/>
-        <v>7.2634600879331809E-2</v>
+        <v>0.10795273768588626</v>
       </c>
       <c r="W11">
         <f t="shared" si="7"/>
